--- a/Grafik_CCEE_SLIVEN1_02_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_02_08_2026.xlsx
@@ -2389,11 +2389,13 @@
       <c r="B85" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C85" s="11" t="n">
-        <v>0</v>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E85" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C85+D85,0))),MIN(1800,MAX(0,D85)))</f>
@@ -2549,13 +2551,11 @@
       <c r="B93" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C93" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E93" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C93+D93,0))),MIN(1800,MAX(0,D93)))</f>

--- a/Grafik_CCEE_SLIVEN1_02_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_02_08_2026.xlsx
@@ -2411,11 +2411,13 @@
       <c r="B86" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C86" s="11" t="n">
-        <v>0</v>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D86" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E86" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C86+D86,0))),MIN(1800,MAX(0,D86)))</f>
@@ -2431,11 +2433,13 @@
       <c r="B87" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C87" s="11" t="n">
-        <v>0</v>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E87" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C87+D87,0))),MIN(1800,MAX(0,D87)))</f>
@@ -2451,11 +2455,13 @@
       <c r="B88" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>0</v>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E88" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C88+D88,0))),MIN(1800,MAX(0,D88)))</f>
@@ -2471,11 +2477,13 @@
       <c r="B89" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>0</v>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D89" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E89" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C89+D89,0))),MIN(1800,MAX(0,D89)))</f>
@@ -2491,11 +2499,13 @@
       <c r="B90" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>0</v>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E90" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C90+D90,0))),MIN(1800,MAX(0,D90)))</f>
@@ -2571,13 +2581,11 @@
       <c r="B94" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C94" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E94" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C94+D94,0))),MIN(1800,MAX(0,D94)))</f>
@@ -2593,13 +2601,11 @@
       <c r="B95" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C95" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E95" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C95+D95,0))),MIN(1800,MAX(0,D95)))</f>
@@ -2615,13 +2621,11 @@
       <c r="B96" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C96" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E96" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C96+D96,0))),MIN(1800,MAX(0,D96)))</f>
@@ -2637,13 +2641,11 @@
       <c r="B97" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C97" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E97" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C97+D97,0))),MIN(1800,MAX(0,D97)))</f>
@@ -2659,13 +2661,11 @@
       <c r="B98" s="1" t="n">
         <v>46236</v>
       </c>
-      <c r="C98" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C98" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E98" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C98+D98,0))),MIN(1800,MAX(0,D98)))</f>
